--- a/Tata_Steel_Credit_Risk_Model.xlsx.xlsx
+++ b/Tata_Steel_Credit_Risk_Model.xlsx.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr updateLinks="always" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ee57e6e14e52454/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ee57e6e14e52454/Documents/GitHub/credit-risk-analysis-tata-steel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="747" documentId="8_{13047485-A380-4C17-9C17-2CBABEED5538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9854B4C5-687C-4A7C-8724-80B141B0274A}"/>
+  <xr:revisionPtr revIDLastSave="749" documentId="8_{13047485-A380-4C17-9C17-2CBABEED5538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A16CA053-831B-497D-9491-3108C5F07157}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F31EEC50-2DF9-41FD-8E7B-28670682E1B2}"/>
   </bookViews>
@@ -684,9 +684,6 @@
     <t>Analyst</t>
   </si>
   <si>
-    <t>— Enter Your Name —</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -697,6 +694,9 @@
   </si>
   <si>
     <t>For academic and analytical purposes only. Not investment advice.</t>
+  </si>
+  <si>
+    <t>HELAN PREETHI M</t>
   </si>
 </sst>
 </file>
@@ -1516,16 +1516,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="32" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="17" fontId="32" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1535,7 +1526,13 @@
     <xf numFmtId="0" fontId="42" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="32" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="43" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1549,12 +1546,6 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="49" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1562,6 +1553,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1570,26 +1570,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="20">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1741,6 +1721,26 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3087,20 +3087,16 @@
 </externalLink>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{41673E72-EDF3-4939-A1C5-BFD4D00464FD}" name="Table1" displayName="Table1" ref="A11:D16" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="A11:D16" xr:uid="{41673E72-EDF3-4939-A1C5-BFD4D00464FD}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{E11BFD8D-4CF8-49B5-8DB8-CB9BF7D16FF0}" name="Ratio" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{ADA68096-E359-4D26-8077-9A5894943539}" name="Value" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{ADA68096-E359-4D26-8077-9A5894943539}" name="Value" dataDxfId="16">
       <calculatedColumnFormula>ROUND(RATIOS!C7,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{583C9B0C-B6BD-416F-BC37-BB5DC8ABAFC8}" name="Weight" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{19A5B357-177B-4C69-B3F8-23BA7E19DD2B}" name="Interpretation" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{583C9B0C-B6BD-416F-BC37-BB5DC8ABAFC8}" name="Weight" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{19A5B357-177B-4C69-B3F8-23BA7E19DD2B}" name="Interpretation" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3471,229 +3467,229 @@
     <row r="1" spans="1:8" ht="15" customHeight="1"/>
     <row r="2" spans="1:8" ht="15" customHeight="1"/>
     <row r="3" spans="1:8" ht="30" customHeight="1">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="99" t="s">
         <v>151</v>
       </c>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="95"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1">
-      <c r="A4" s="95"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="95"/>
+      <c r="A4" s="97"/>
+      <c r="B4" s="97"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1">
-      <c r="A5" s="95"/>
-      <c r="B5" s="95"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="95"/>
-      <c r="H5" s="95"/>
+      <c r="A5" s="97"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1">
-      <c r="A6" s="95"/>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
+      <c r="A6" s="97"/>
+      <c r="B6" s="97"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="97"/>
     </row>
     <row r="7" spans="1:8" ht="17.399999999999999">
-      <c r="A7" s="101" t="s">
+      <c r="A7" s="100" t="s">
         <v>152</v>
       </c>
-      <c r="B7" s="95"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="95"/>
+      <c r="B7" s="97"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
     </row>
     <row r="8" spans="1:8" ht="6" customHeight="1">
-      <c r="A8" s="102"/>
-      <c r="B8" s="95"/>
-      <c r="C8" s="95"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
+      <c r="A8" s="101"/>
+      <c r="B8" s="97"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="97"/>
     </row>
     <row r="9" spans="1:8" ht="19.95" customHeight="1"/>
     <row r="10" spans="1:8" ht="22.05" customHeight="1">
-      <c r="A10" s="103" t="s">
+      <c r="A10" s="102" t="s">
         <v>153</v>
       </c>
-      <c r="B10" s="95"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="95"/>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="95"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="97"/>
+      <c r="H10" s="97"/>
     </row>
     <row r="11" spans="1:8" ht="28.2">
-      <c r="A11" s="104" t="str">
+      <c r="A11" s="103" t="str">
         <f>[1]INPUTS!B2</f>
         <v>Tata Steel Limited</v>
       </c>
-      <c r="B11" s="95"/>
-      <c r="C11" s="95"/>
-      <c r="D11" s="95"/>
-      <c r="E11" s="95"/>
-      <c r="F11" s="95"/>
-      <c r="G11" s="95"/>
-      <c r="H11" s="95"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="97"/>
+      <c r="F11" s="97"/>
+      <c r="G11" s="97"/>
+      <c r="H11" s="97"/>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1"/>
     <row r="13" spans="1:8" ht="24" customHeight="1">
-      <c r="B13" s="105" t="s">
+      <c r="B13" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="95"/>
-      <c r="D13" s="106" t="str">
+      <c r="C13" s="97"/>
+      <c r="D13" s="98" t="str">
         <f>[1]INPUTS!B3</f>
         <v>TATASTEEL</v>
       </c>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
+      <c r="E13" s="97"/>
+      <c r="F13" s="97"/>
+      <c r="G13" s="97"/>
     </row>
     <row r="14" spans="1:8" ht="24" customHeight="1">
-      <c r="B14" s="105" t="s">
+      <c r="B14" s="96" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="95"/>
-      <c r="D14" s="106" t="str">
-        <f ca="1">TEXT([1]INPUTS!B4,"DD-MM-YYYY")</f>
+      <c r="C14" s="97"/>
+      <c r="D14" s="98" t="str">
+        <f>TEXT([1]INPUTS!B4,"DD-MM-YYYY")</f>
         <v>07-06-2026</v>
       </c>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
+      <c r="E14" s="97"/>
+      <c r="F14" s="97"/>
+      <c r="G14" s="97"/>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1">
-      <c r="B15" s="105" t="s">
+      <c r="B15" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="95"/>
-      <c r="D15" s="106" t="str">
+      <c r="C15" s="97"/>
+      <c r="D15" s="98" t="str">
         <f>TEXT([1]INPUTS!B6,"MMM-YYYY")</f>
         <v>Mar-2026</v>
       </c>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
+      <c r="E15" s="97"/>
+      <c r="F15" s="97"/>
+      <c r="G15" s="97"/>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1">
-      <c r="B16" s="105" t="s">
+      <c r="B16" s="96" t="s">
         <v>154</v>
       </c>
-      <c r="C16" s="95"/>
-      <c r="D16" s="106" t="str">
+      <c r="C16" s="97"/>
+      <c r="D16" s="98" t="str">
         <f>[1]INPUTS!B5</f>
         <v>Crores INR</v>
       </c>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
+      <c r="E16" s="97"/>
+      <c r="F16" s="97"/>
+      <c r="G16" s="97"/>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1">
-      <c r="B17" s="105" t="s">
+      <c r="B17" s="96" t="s">
         <v>155</v>
       </c>
-      <c r="C17" s="95"/>
-      <c r="D17" s="106" t="s">
+      <c r="C17" s="97"/>
+      <c r="D17" s="98" t="s">
         <v>156</v>
       </c>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
+      <c r="E17" s="97"/>
+      <c r="F17" s="97"/>
+      <c r="G17" s="97"/>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1">
-      <c r="B18" s="105" t="s">
+      <c r="B18" s="96" t="s">
         <v>157</v>
       </c>
-      <c r="C18" s="95"/>
-      <c r="D18" s="106" t="s">
+      <c r="C18" s="97"/>
+      <c r="D18" s="98" t="s">
         <v>158</v>
       </c>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
+      <c r="E18" s="97"/>
+      <c r="F18" s="97"/>
+      <c r="G18" s="97"/>
     </row>
     <row r="19" spans="1:8" ht="24" customHeight="1">
-      <c r="B19" s="105" t="s">
+      <c r="B19" s="96" t="s">
         <v>159</v>
       </c>
-      <c r="C19" s="95"/>
-      <c r="D19" s="106" t="s">
+      <c r="C19" s="97"/>
+      <c r="D19" s="98" t="s">
+        <v>164</v>
+      </c>
+      <c r="E19" s="97"/>
+      <c r="F19" s="97"/>
+      <c r="G19" s="97"/>
+    </row>
+    <row r="20" spans="1:8" ht="24" customHeight="1">
+      <c r="B20" s="96" t="s">
         <v>160</v>
       </c>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-    </row>
-    <row r="20" spans="1:8" ht="24" customHeight="1">
-      <c r="B20" s="105" t="s">
+      <c r="C20" s="97"/>
+      <c r="D20" s="98" t="s">
         <v>161</v>
       </c>
-      <c r="C20" s="95"/>
-      <c r="D20" s="106" t="s">
-        <v>162</v>
-      </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
+      <c r="E20" s="97"/>
+      <c r="F20" s="97"/>
+      <c r="G20" s="97"/>
     </row>
     <row r="22" spans="1:8" ht="19.95" customHeight="1"/>
     <row r="23" spans="1:8" ht="28.05" customHeight="1">
-      <c r="B23" s="107" t="s">
-        <v>163</v>
-      </c>
-      <c r="C23" s="95"/>
-      <c r="D23" s="95"/>
-      <c r="E23" s="95"/>
-      <c r="F23" s="95"/>
-      <c r="G23" s="95"/>
+      <c r="B23" s="104" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23" s="97"/>
+      <c r="D23" s="97"/>
+      <c r="E23" s="97"/>
+      <c r="F23" s="97"/>
+      <c r="G23" s="97"/>
     </row>
     <row r="24" spans="1:8" ht="16.8">
-      <c r="B24" s="108" t="str">
+      <c r="B24" s="105" t="str">
         <f>[1]ZSCORE!B5&amp;"  |  "&amp;[1]ZSCORE!B7&amp;"  |  "&amp;[1]ZSCORE!B11</f>
         <v>2.07930256479436  |  GREY ZONE — Monitor closely  |  BB/B</v>
       </c>
-      <c r="C24" s="95"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
-      <c r="F24" s="95"/>
-      <c r="G24" s="95"/>
+      <c r="C24" s="97"/>
+      <c r="D24" s="97"/>
+      <c r="E24" s="97"/>
+      <c r="F24" s="97"/>
+      <c r="G24" s="97"/>
     </row>
     <row r="26" spans="1:8" ht="18" customHeight="1">
-      <c r="A26" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="B26" s="95"/>
-      <c r="C26" s="95"/>
-      <c r="D26" s="95"/>
-      <c r="E26" s="95"/>
-      <c r="F26" s="95"/>
-      <c r="G26" s="95"/>
-      <c r="H26" s="95"/>
+      <c r="A26" s="106" t="s">
+        <v>163</v>
+      </c>
+      <c r="B26" s="97"/>
+      <c r="C26" s="97"/>
+      <c r="D26" s="97"/>
+      <c r="E26" s="97"/>
+      <c r="F26" s="97"/>
+      <c r="G26" s="97"/>
+      <c r="H26" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -3714,13 +3710,13 @@
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:G16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:G13"/>
     <mergeCell ref="A3:H6"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:G13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3772,7 +3768,7 @@
       </c>
       <c r="B4" s="28">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>57</v>
@@ -3917,7 +3913,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B7:B17">
-    <cfRule type="containsBlanks" dxfId="14" priority="1">
+    <cfRule type="containsBlanks" dxfId="13" priority="1">
       <formula>LEN(TRIM(B7))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3942,16 +3938,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="107" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="34" t="s">
@@ -4118,14 +4114,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="108" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
     </row>
     <row r="4" spans="1:6" ht="15" thickBot="1"/>
     <row r="5" spans="1:6" ht="15" thickBot="1">
@@ -4182,38 +4178,38 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
-    <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="DISTRESS ZONE ">
+    <cfRule type="containsText" dxfId="12" priority="9" operator="containsText" text="DISTRESS ZONE ">
       <formula>NOT(ISERROR(SEARCH("DISTRESS ZONE ",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="10" operator="containsText" text="GREY ZONE ">
+    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="GREY ZONE ">
       <formula>NOT(ISERROR(SEARCH("GREY ZONE ",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="SAFE ZONE ">
+    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="SAFE ZONE ">
       <formula>NOT(ISERROR(SEARCH("SAFE ZONE ",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="D">
+    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="D">
       <formula>NOT(ISERROR(SEARCH("D",B11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="CCC/CC ">
+    <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="CCC/CC ">
       <formula>NOT(ISERROR(SEARCH("CCC/CC ",B11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="BB/B ">
+    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="BB/B ">
       <formula>NOT(ISERROR(SEARCH("BB/B ",B11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="A/BBB ">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="A/BBB ">
       <formula>NOT(ISERROR(SEARCH("A/BBB ",B11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="AAA/AA ">
+    <cfRule type="containsText" dxfId="5" priority="8" operator="containsText" text="AAA/AA ">
       <formula>NOT(ISERROR(SEARCH("AAA/AA ",B11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:D12">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="GREY ZONE ">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="GREY ZONE ">
       <formula>NOT(ISERROR(SEARCH("GREY ZONE ",B12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="DISTRESS ZONE ">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="DISTRESS ZONE ">
       <formula>NOT(ISERROR(SEARCH("DISTRESS ZONE ",B12)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4235,17 +4231,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="108" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
     </row>
     <row r="3" spans="1:10">
       <c r="B3" s="41" t="s">
@@ -4445,7 +4441,7 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="B12:D12">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="GREY ZONE">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="GREY ZONE">
       <formula>NOT(ISERROR(SEARCH("GREY ZONE",B12)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4477,17 +4473,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16.8">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="109" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
     </row>
     <row r="2" spans="1:9" s="51" customFormat="1" ht="26.4">
       <c r="A2" s="52" t="s">
@@ -4706,17 +4702,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.95" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="93" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
       <c r="J1" s="73"/>
     </row>
     <row r="4" spans="1:10" ht="19.95" customHeight="1">
@@ -4799,7 +4795,7 @@
       <c r="D8" s="75" t="s">
         <v>148</v>
       </c>
-      <c r="E8" s="99">
+      <c r="E8" s="92">
         <f>INPUTS!B6</f>
         <v>46082</v>
       </c>
@@ -4809,7 +4805,7 @@
       </c>
       <c r="H8" s="83">
         <f ca="1">INPUTS!B4</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="I8" s="75"/>
       <c r="J8" s="75"/>
@@ -4968,74 +4964,74 @@
       </c>
     </row>
     <row r="30" spans="2:10" ht="19.95" customHeight="1">
-      <c r="B30" s="97" t="s">
+      <c r="B30" s="94" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="97"/>
-      <c r="D30" s="97"/>
-      <c r="E30" s="97"/>
-      <c r="F30" s="97"/>
-      <c r="G30" s="97"/>
-      <c r="H30" s="97"/>
-      <c r="I30" s="97"/>
-      <c r="J30" s="97"/>
+      <c r="C30" s="94"/>
+      <c r="D30" s="94"/>
+      <c r="E30" s="94"/>
+      <c r="F30" s="94"/>
+      <c r="G30" s="94"/>
+      <c r="H30" s="94"/>
+      <c r="I30" s="94"/>
+      <c r="J30" s="94"/>
     </row>
     <row r="31" spans="2:10" ht="19.95" customHeight="1">
-      <c r="B31" s="97"/>
-      <c r="C31" s="97"/>
-      <c r="D31" s="97"/>
-      <c r="E31" s="97"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="97"/>
-      <c r="H31" s="97"/>
-      <c r="I31" s="97"/>
-      <c r="J31" s="97"/>
+      <c r="B31" s="94"/>
+      <c r="C31" s="94"/>
+      <c r="D31" s="94"/>
+      <c r="E31" s="94"/>
+      <c r="F31" s="94"/>
+      <c r="G31" s="94"/>
+      <c r="H31" s="94"/>
+      <c r="I31" s="94"/>
+      <c r="J31" s="94"/>
     </row>
     <row r="32" spans="2:10" ht="19.95" customHeight="1">
-      <c r="B32" s="97"/>
-      <c r="C32" s="97"/>
-      <c r="D32" s="97"/>
-      <c r="E32" s="97"/>
-      <c r="F32" s="97"/>
-      <c r="G32" s="97"/>
-      <c r="H32" s="97"/>
-      <c r="I32" s="97"/>
-      <c r="J32" s="97"/>
+      <c r="B32" s="94"/>
+      <c r="C32" s="94"/>
+      <c r="D32" s="94"/>
+      <c r="E32" s="94"/>
+      <c r="F32" s="94"/>
+      <c r="G32" s="94"/>
+      <c r="H32" s="94"/>
+      <c r="I32" s="94"/>
+      <c r="J32" s="94"/>
     </row>
     <row r="33" spans="2:10" ht="19.95" customHeight="1">
-      <c r="B33" s="97"/>
-      <c r="C33" s="97"/>
-      <c r="D33" s="97"/>
-      <c r="E33" s="97"/>
-      <c r="F33" s="97"/>
-      <c r="G33" s="97"/>
-      <c r="H33" s="97"/>
-      <c r="I33" s="97"/>
-      <c r="J33" s="97"/>
+      <c r="B33" s="94"/>
+      <c r="C33" s="94"/>
+      <c r="D33" s="94"/>
+      <c r="E33" s="94"/>
+      <c r="F33" s="94"/>
+      <c r="G33" s="94"/>
+      <c r="H33" s="94"/>
+      <c r="I33" s="94"/>
+      <c r="J33" s="94"/>
     </row>
     <row r="35" spans="2:10" ht="19.95" customHeight="1">
-      <c r="B35" s="98" t="s">
+      <c r="B35" s="95" t="s">
         <v>150</v>
       </c>
-      <c r="C35" s="98"/>
-      <c r="D35" s="98"/>
-      <c r="E35" s="98"/>
-      <c r="F35" s="98"/>
-      <c r="G35" s="98"/>
-      <c r="H35" s="98"/>
-      <c r="I35" s="98"/>
-      <c r="J35" s="98"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="95"/>
+      <c r="E35" s="95"/>
+      <c r="F35" s="95"/>
+      <c r="G35" s="95"/>
+      <c r="H35" s="95"/>
+      <c r="I35" s="95"/>
+      <c r="J35" s="95"/>
     </row>
     <row r="36" spans="2:10" ht="19.95" customHeight="1">
-      <c r="B36" s="98"/>
-      <c r="C36" s="98"/>
-      <c r="D36" s="98"/>
-      <c r="E36" s="98"/>
-      <c r="F36" s="98"/>
-      <c r="G36" s="98"/>
-      <c r="H36" s="98"/>
-      <c r="I36" s="98"/>
-      <c r="J36" s="98"/>
+      <c r="B36" s="95"/>
+      <c r="C36" s="95"/>
+      <c r="D36" s="95"/>
+      <c r="E36" s="95"/>
+      <c r="F36" s="95"/>
+      <c r="G36" s="95"/>
+      <c r="H36" s="95"/>
+      <c r="I36" s="95"/>
+      <c r="J36" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5631,7 +5627,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="M2:M9">
-    <cfRule type="containsBlanks" dxfId="1" priority="1">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(M2))=0</formula>
     </cfRule>
   </conditionalFormatting>
